--- a/data/production/production_2026-W43.xlsx
+++ b/data/production/production_2026-W43.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -483,22 +483,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU-362227</t>
+          <t>CM-237250</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Felix Tanaka</t>
+          <t>Isaac Holloway</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -507,43 +507,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2454.98</v>
+        <v>2648.24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LF-395818</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Clara Pryor</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$642.05</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -551,33 +519,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AU-819265</t>
+          <t>CM-953354</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mila Novak</t>
+          <t>Adrian Okafor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Auto</t>
+          <t xml:space="preserve">Commercial </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>$1,136.55</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6864.95</v>
       </c>
     </row>
     <row r="7">
@@ -586,22 +552,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CM-427270</t>
+          <t>AU-241898</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lena Quill</t>
+          <t>Elena Novak</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -610,7 +576,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6886.36</v>
+        <v>1096.86</v>
       </c>
     </row>
     <row r="8">
@@ -619,31 +585,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CM-769536</t>
+          <t>HO-446220</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4246.31</v>
+          <t xml:space="preserve">Renewal </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>$1,447.33</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -657,26 +625,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HO-144033</t>
+          <t>HO-790003</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Maria Moreau</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t xml:space="preserve">Home </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2757.2</v>
+        <v>2697.03</v>
       </c>
     </row>
     <row r="10">
@@ -685,22 +653,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRIYA RAMAN</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LF-311895</t>
+          <t>AU-534360</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alma Ashby</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Life </t>
+          <t xml:space="preserve">Auto </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -709,31 +677,31 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>939.41</v>
+        <v>1332.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AU-504048</t>
+          <t>HO-693705</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Grace Delgado</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -742,7 +710,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1307.52</v>
+        <v>2207.35</v>
       </c>
     </row>
     <row r="12">
@@ -751,22 +719,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AU-377860</t>
+          <t>HO-350771</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hannah Haines</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -775,7 +743,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1433.48</v>
+        <v>1984.32</v>
       </c>
     </row>
     <row r="13">
@@ -784,31 +752,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>maya chen</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AU-460589</t>
+          <t>CM-153799</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Victor Petrov</t>
+          <t>Ruby Sorensen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1684.97</v>
+        <v>6408.77</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +785,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AU-852715</t>
+          <t>AU-793692</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nora Ashby</t>
+          <t>Ivy Okafor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -837,46 +805,46 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>$1,365.92</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1188.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AU-398301</t>
+          <t>LF-557718</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ivy Okafor</t>
+          <t>Felix Tanaka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>997.34</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>$2,401.31</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -885,17 +853,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AU-997287</t>
+          <t>AU-751111</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lena Quill</t>
+          <t>Leah Okafor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -909,7 +877,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1338.52</v>
+        <v>874.78</v>
       </c>
     </row>
     <row r="17">
@@ -918,65 +886,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t xml:space="preserve"> Aisha Bello</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LF-950472</t>
+          <t>CM-383325</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Maria Duarte</t>
+          <t>Jonah Quill</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Life </t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1074.73</v>
+        <v>4569.12</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Luis Ortega</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CM-489438</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Theo Moreau</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>6248.75</v>
-      </c>
+      <c r="A18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -984,31 +922,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AU-726003</t>
+          <t>HO-473230</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ivy Hartley</t>
+          <t>Victor Petrov</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>2048.8</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>$2,265.51</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1017,31 +957,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HO-136862</t>
+          <t>LF-664425</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1602.73</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>$625.10</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1055,17 +997,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HO-263281</t>
+          <t>AU-262280</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Maria Duarte</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1074,7 +1016,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1868.14</v>
+        <v>1220.09</v>
       </c>
     </row>
     <row r="22">
@@ -1083,31 +1025,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LF-555251</t>
+          <t>HO-588433</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Owen Sorensen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1043.21</v>
+        <v>2040.92</v>
       </c>
     </row>
     <row r="23">
@@ -1116,83 +1058,83 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AU-181721</t>
+          <t>HO-792322</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Owen Sorensen</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1005.58</v>
+        <v>2890.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CM-209159</t>
+          <t>LF-889681</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Olivia Delgado</t>
+          <t>Maria Lopez</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commercial </t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7066.58</v>
+        <v>1264.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AU-359168</t>
+          <t>AU-434010</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Alma Ashby</t>
+          <t>Elena Mbeki</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1202,63 +1144,65 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>2303.46</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>$1,176.80</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>priya raman</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HO-258003</t>
+          <t>CM-471156</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Maria Duarte</t>
+          <t>Olivia Hartley</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Renewal </t>
+          <t>New</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1593</v>
+        <v>6670.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HO-892170</t>
+          <t>HO-168450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Felix Tanaka</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1268,16 +1212,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1117.47</v>
+        <v>2124.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1286,12 +1230,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HO-961957</t>
+          <t>HO-891943</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hannah Haines</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1305,7 +1249,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2661.3</v>
+        <v>2301.51</v>
       </c>
     </row>
     <row r="29">
@@ -1314,55 +1258,55 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LF-939930</t>
+          <t>AU-920712</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Samuel Brennan</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2180.95</v>
+        <v>995.6799999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AU-324319</t>
+          <t>HO-457386</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Zoe Marsh</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1371,31 +1315,31 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1261.08</v>
+        <v>1330.82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t xml:space="preserve">Tom Becker </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HO-885587</t>
+          <t>AU-315590</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sofia Pryor</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1403,41 +1347,43 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>1596.57</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>$1,006.01</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LF-453907</t>
+          <t>AU-924424</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Olivia Delgado</t>
+          <t>Nora Ruiz</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1644.93</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="33">
@@ -1446,31 +1392,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HO-262230</t>
+          <t>AU-541892</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Alma Ashby</t>
+          <t>Theo Moreau</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>2298.4</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>$2,480.19</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1479,31 +1427,33 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CM-158760</t>
+          <t>AU-417219</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>8936.389999999999</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>$1,057.80</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1517,17 +1467,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AU-338161</t>
+          <t>HO-832701</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1535,10 +1485,8 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>$1,420.75</t>
-        </is>
+      <c r="G35" t="n">
+        <v>1603.62</v>
       </c>
     </row>
     <row r="36">
@@ -1547,141 +1495,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HO-385647</t>
+          <t>CM-620964</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ruby Sorensen</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Renewal</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2900.38</v>
+        <v>3170.62</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46318</v>
-      </c>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maya Chen </t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HO-885290</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Felix Lindqvist</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Renewal</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2171.14</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AU-507475</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Samuel Ruiz</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1953.66</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LF-378727</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Leah Novak</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>710.77</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>83899.38</v>
+        <v>72318.03</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +1582,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HO-136862</t>
+          <t>HO-446220</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1742,7 +1591,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1458.28</v>
+        <v>1343.54</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1758,16 +1607,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HO-385647</t>
+          <t>AU-241898</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2928.89</v>
+        <v>1123.32</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1783,7 +1632,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HO-885290</t>
+          <t>HO-792322</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1792,7 +1641,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2058.74</v>
+        <v>2591.91</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1803,21 +1652,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HO-258003</t>
+          <t>LF-889681</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1588.9</v>
+        <v>1176.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1828,25 +1677,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CM-489438</t>
+          <t>LF-718572</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5739.57</v>
+        <v>1084.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1707,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CM-158760</t>
+          <t>CM-953354</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1867,7 +1716,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8685.690000000001</v>
+        <v>6706.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1883,16 +1732,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AU-362227</t>
+          <t>CM-153799</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2243.55</v>
+        <v>6517.99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1903,21 +1752,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AU-359168</t>
+          <t>HO-168450</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2362.46</v>
+        <v>2187.28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1933,16 +1782,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CM-427270</t>
+          <t>HO-790003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6929.38</v>
+        <v>2410.45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1958,7 +1807,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CM-769536</t>
+          <t>CM-620964</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1967,7 +1816,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4146.53</v>
+        <v>2936.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1978,21 +1827,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LF-555251</t>
+          <t>AU-924424</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1048.34</v>
+        <v>2244.45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2008,7 +1857,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AU-507475</t>
+          <t>AU-315590</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2017,7 +1866,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1862.63</v>
+        <v>1019.31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2033,16 +1882,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AU-852715</t>
+          <t>HO-693705</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1231.08</v>
+        <v>1984.48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2058,7 +1907,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AU-504048</t>
+          <t>AU-541892</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2067,7 +1916,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1246.53</v>
+        <v>2350.61</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2083,16 +1932,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HO-885587</t>
+          <t>AU-751111</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1475.69</v>
+        <v>901.3099999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2108,20 +1957,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AU-569237</t>
+          <t>HO-473230</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2342.48</v>
+        <v>2204.85</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
@@ -2133,7 +1982,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AU-398301</t>
+          <t>AU-920712</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2142,7 +1991,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>951.99</v>
+        <v>900.52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2158,16 +2007,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AU-997287</t>
+          <t>CM-237250</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1232.83</v>
+        <v>2725.79</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
